--- a/nr-update-valueset/ig/ValueSet-as-vs-intern-id-systems.xlsx
+++ b/nr-update-valueset/ig/ValueSet-as-vs-intern-id-systems.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-update-valueset/ig/ValueSet-as-vs-intern-id-systems.xlsx
+++ b/nr-update-valueset/ig/ValueSet-as-vs-intern-id-systems.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from Internal Id Syst" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from AS CodeSystem In" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Internal Id Systems VS</t>
+    <t>AS ValueSet Internal Identifier Systems</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Systèmes des identifiants internes</t>
+    <t>ValueSet contenant les identifiants internes</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-update-valueset/ig/ValueSet-as-vs-intern-id-systems.xlsx
+++ b/nr-update-valueset/ig/ValueSet-as-vs-intern-id-systems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
